--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -3994,7 +3994,7 @@
         <x:v>统计日期</x:v>
       </x:c>
       <x:c r="B3" s="91">
-        <x:v>46288</x:v>
+        <x:v>46289</x:v>
       </x:c>
       <x:c r="C3" s="2"/>
       <x:c r="D3" s="2"/>
@@ -4092,7 +4092,7 @@
       </x:c>
       <x:c r="F6" s="58">
         <x:f>'_数据接口'!B26</x:f>
-        <x:v>0.0259259259259259</x:v>
+        <x:v>0.025925925925925925</x:v>
       </x:c>
       <x:c r="G6" s="57">
         <x:f>'_数据接口'!B27</x:f>
@@ -4100,7 +4100,7 @@
       </x:c>
       <x:c r="H6" s="57">
         <x:f>'_数据接口'!B28</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I6" s="57">
         <x:f>'_数据接口'!B33</x:f>
@@ -4178,19 +4178,16 @@
     <x:row r="9" spans="1:14" ht="26" customHeight="1">
       <x:c r="A9" s="64">
         <x:f>'_数据接口'!B26</x:f>
-        <x:v>0.0259259259259259</x:v>
+        <x:v>0.025925925925925925</x:v>
       </x:c>
       <x:c r="B9" s="65">
         <x:f>'_数据接口'!B17</x:f>
-        <x:v>5433</x:v>
       </x:c>
       <x:c r="C9" s="89">
         <x:f>'_数据接口'!B18</x:f>
-        <x:v>7697700</x:v>
       </x:c>
       <x:c r="D9" s="90">
         <x:f>'_数据接口'!B19</x:f>
-        <x:v>1416.84152401988</x:v>
       </x:c>
       <x:c r="E9" s="20">
         <x:f>'_数据接口'!B29</x:f>
@@ -4531,7 +4528,6 @@
       <x:c r="H19" s="2"/>
       <x:c r="I19" s="2">
         <x:f>'_数据接口'!B39</x:f>
-        <x:v>6</x:v>
       </x:c>
       <x:c r="J19" s="2">
         <x:f>'_数据接口'!B40</x:f>
@@ -4543,7 +4539,6 @@
       </x:c>
       <x:c r="L19" s="2">
         <x:f>'_数据接口'!B42</x:f>
-        <x:v>7</x:v>
       </x:c>
       <x:c r="M19" s="2"/>
       <x:c r="N19" s="77"/>
@@ -4994,7 +4989,7 @@
     <x:row r="2" spans="1:12" ht="20" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:f>"数据截止"&amp;'_数据接口'!B5&amp;"。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。"</x:f>
-        <x:v>数据截止2026-09-23。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。</x:v>
+        <x:v>数据截止2026-09-24。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -5028,7 +5023,7 @@
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:f>'_数据接口'!B5</x:f>
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="7" t="s">
@@ -5108,7 +5103,7 @@
       </x:c>
       <x:c r="D7" s="20">
         <x:f>'_数据接口'!B28</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="5">
         <x:f>'_数据接口'!B33</x:f>
@@ -5662,130 +5657,130 @@
     </x:row>
     <x:row r="5" spans="1:10" ht="34" customHeight="1">
       <x:c r="A5" s="9" t="str">
-        <x:v>项目总控台账</x:v>
+        <x:v>G15-会前签认跟踪-20260924-V1.xlsx</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>T008</x:v>
+        <x:v>MODULE-CODE</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>汇编可研报告并组织评审</x:v>
+        <x:v>模块编号检查</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
         <x:v>项目经理</x:v>
       </x:c>
-      <x:c r="E5" s="95">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F5" s="95">
-        <x:v>46283</x:v>
+      <x:c r="E5" s="95" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F5" s="95" t="str">
+        <x:v/>
       </x:c>
       <x:c r="G5" s="9" t="str">
-        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
+        <x:v>缺少_data接口工作表</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
-        <x:v>需整改</x:v>
+        <x:v>阻断</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
-        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
-      </x:c>
-      <x:c r="J5" s="9">
-        <x:v>11</x:v>
+        <x:v>补充_data接口并填写模块编号</x:v>
+      </x:c>
+      <x:c r="J5" s="9" t="str">
+        <x:v>-</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10" ht="34" customHeight="1">
       <x:c r="A6" s="9" t="str">
-        <x:v>项目总控台账</x:v>
+        <x:v>安全合规会签清单-20260924-V1.xlsx</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>T011</x:v>
+        <x:v>MODULE-CODE</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>盘点既有系统、接口与数据</x:v>
+        <x:v>模块编号检查</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>技术经理</x:v>
-      </x:c>
-      <x:c r="E6" s="95">
-        <x:v>46120</x:v>
-      </x:c>
-      <x:c r="F6" s="95">
-        <x:v>46147</x:v>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="E6" s="95" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F6" s="95" t="str">
+        <x:v/>
       </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
+        <x:v>缺少_data接口工作表</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>需整改</x:v>
+        <x:v>阻断</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
-        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
-      </x:c>
-      <x:c r="J6" s="9">
-        <x:v>14</x:v>
+        <x:v>补充_data接口并填写模块编号</x:v>
+      </x:c>
+      <x:c r="J6" s="9" t="str">
+        <x:v>-</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10" ht="34" customHeight="1">
       <x:c r="A7" s="9" t="str">
-        <x:v>项目总控台账</x:v>
+        <x:v>厂商报价对比-20260924-V1.xlsx</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>T012</x:v>
+        <x:v>MODULE-CODE</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>访谈业务部门并形成痛点清单</x:v>
+        <x:v>模块编号检查</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>产品经理</x:v>
-      </x:c>
-      <x:c r="E7" s="95">
-        <x:v>46148</x:v>
-      </x:c>
-      <x:c r="F7" s="95">
-        <x:v>46175</x:v>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="E7" s="95" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F7" s="95" t="str">
+        <x:v/>
       </x:c>
       <x:c r="G7" s="9" t="str">
-        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
+        <x:v>缺少_data接口工作表</x:v>
       </x:c>
       <x:c r="H7" s="9" t="str">
-        <x:v>需整改</x:v>
+        <x:v>阻断</x:v>
       </x:c>
       <x:c r="I7" s="9" t="str">
-        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
-      </x:c>
-      <x:c r="J7" s="9">
-        <x:v>15</x:v>
+        <x:v>补充_data接口并填写模块编号</x:v>
+      </x:c>
+      <x:c r="J7" s="9" t="str">
+        <x:v>-</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10" ht="34" customHeight="1">
       <x:c r="A8" s="9" t="str">
-        <x:v>项目总控台账</x:v>
+        <x:v>POC评分表-20260924-V1.xlsx</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>T013</x:v>
+        <x:v>MODULE-CODE</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>确认现状流程、问题与改进机会基线</x:v>
+        <x:v>模块编号检查</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
         <x:v>项目经理</x:v>
       </x:c>
-      <x:c r="E8" s="95">
-        <x:v>46176</x:v>
-      </x:c>
-      <x:c r="F8" s="95">
-        <x:v>46203</x:v>
+      <x:c r="E8" s="95" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F8" s="95" t="str">
+        <x:v/>
       </x:c>
       <x:c r="G8" s="9" t="str">
-        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
+        <x:v>缺少_data接口工作表</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>需整改</x:v>
+        <x:v>阻断</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
-        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
-      </x:c>
-      <x:c r="J8" s="9">
-        <x:v>16</x:v>
+        <x:v>补充_data接口并填写模块编号</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="str">
+        <x:v>-</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10" ht="34" customHeight="1">
@@ -5793,19 +5788,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>T014</x:v>
+        <x:v>T008</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>制定项目治理、会议与报告机制</x:v>
+        <x:v>汇编可研报告并组织评审</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
         <x:v>项目经理</x:v>
       </x:c>
       <x:c r="E9" s="95">
-        <x:v>46204</x:v>
+        <x:v>46238</x:v>
       </x:c>
       <x:c r="F9" s="95">
-        <x:v>46215</x:v>
+        <x:v>46283</x:v>
       </x:c>
       <x:c r="G9" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5817,7 +5812,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J9" s="9">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10" ht="34" customHeight="1">
@@ -5825,19 +5820,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>T015</x:v>
+        <x:v>T011</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>制定需求分级、跟踪与变更规范</x:v>
+        <x:v>盘点既有系统、接口与数据</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E10" s="95">
-        <x:v>46216</x:v>
+        <x:v>46120</x:v>
       </x:c>
       <x:c r="F10" s="95">
-        <x:v>46227</x:v>
+        <x:v>46147</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5849,7 +5844,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J10" s="9">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10" ht="34" customHeight="1">
@@ -5857,19 +5852,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>T016</x:v>
+        <x:v>T012</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>制定设计、编码与代码评审规范</x:v>
+        <x:v>访谈业务部门并形成痛点清单</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="E11" s="95">
-        <x:v>46228</x:v>
+        <x:v>46148</x:v>
       </x:c>
       <x:c r="F11" s="95">
-        <x:v>46240</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5881,7 +5876,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J11" s="9">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10" ht="34" customHeight="1">
@@ -5889,19 +5884,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>T017</x:v>
+        <x:v>T013</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>制定测试、缺陷与质量门禁规范</x:v>
+        <x:v>确认现状流程、问题与改进机会基线</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="E12" s="95">
-        <x:v>46241</x:v>
+        <x:v>46176</x:v>
       </x:c>
       <x:c r="F12" s="95">
-        <x:v>46252</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5913,7 +5908,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J12" s="9">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10" ht="34" customHeight="1">
@@ -5921,19 +5916,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>T018</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>制定配置、发布与文档归档规范</x:v>
+        <x:v>制定项目治理、会议与报告机制</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="E13" s="95">
-        <x:v>46253</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="F13" s="95">
-        <x:v>46265</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5945,7 +5940,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J13" s="9">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10" ht="34" customHeight="1">
@@ -5953,19 +5948,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>T019</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>完成系统分层、模块与服务边界设计</x:v>
+        <x:v>制定需求分级、跟踪与变更规范</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="E14" s="95">
-        <x:v>46204</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="F14" s="95">
-        <x:v>46218</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5977,7 +5972,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J14" s="9">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10" ht="34" customHeight="1">
@@ -5985,19 +5980,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>T020</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>完成主数据、交易数据与分析数据架构</x:v>
+        <x:v>制定设计、编码与代码评审规范</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
         <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E15" s="95">
-        <x:v>46219</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="F15" s="95">
-        <x:v>46233</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="G15" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6009,7 +6004,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J15" s="9">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10" ht="34" customHeight="1">
@@ -6017,19 +6012,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>T021</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>完成内部及外部接口总体架构</x:v>
+        <x:v>制定测试、缺陷与质量门禁规范</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="E16" s="95">
-        <x:v>46234</x:v>
+        <x:v>46241</x:v>
       </x:c>
       <x:c r="F16" s="95">
-        <x:v>46249</x:v>
+        <x:v>46252</x:v>
       </x:c>
       <x:c r="G16" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6041,7 +6036,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J16" s="9">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10" ht="34" customHeight="1">
@@ -6049,19 +6044,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>T022</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>完成身份、权限、审计与数据安全设计</x:v>
+        <x:v>制定配置、发布与文档归档规范</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="E17" s="95">
-        <x:v>46250</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="F17" s="95">
-        <x:v>46264</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="G17" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6073,7 +6068,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J17" s="9">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10" ht="34" customHeight="1">
@@ -6081,19 +6076,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>T023</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>完成环境、网络、容灾和DevOps设计</x:v>
+        <x:v>完成系统分层、模块与服务边界设计</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E18" s="95">
-        <x:v>46265</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="F18" s="95">
-        <x:v>46279</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6105,7 +6100,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J18" s="9">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10" ht="34" customHeight="1">
@@ -6113,19 +6108,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>T025</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>编制CA、电子文档、BI报表POC方案与评分标准</x:v>
+        <x:v>完成主数据、交易数据与分析数据架构</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
         <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E19" s="95">
-        <x:v>46249</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="F19" s="95">
-        <x:v>46253</x:v>
+        <x:v>46233</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6137,7 +6132,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J19" s="9">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10" ht="34" customHeight="1">
@@ -6145,19 +6140,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>T026</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>验证证书签发、身份认证和证书管理</x:v>
+        <x:v>完成内部及外部接口总体架构</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
         <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="E20" s="95">
-        <x:v>46254</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="F20" s="95">
-        <x:v>46258</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6169,7 +6164,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J20" s="9">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="34" customHeight="1">
@@ -6177,19 +6172,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>T027</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>验证电子签名、验签、时间戳和审计追溯</x:v>
+        <x:v>完成身份、权限、审计与数据安全设计</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E21" s="95">
-        <x:v>46259</x:v>
+        <x:v>46250</x:v>
       </x:c>
       <x:c r="F21" s="95">
-        <x:v>46263</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6201,7 +6196,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J21" s="9">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10" ht="34" customHeight="1">
@@ -6209,19 +6204,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>T028</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>验证模板生成、在线预览和格式转换</x:v>
+        <x:v>完成环境、网络、容灾和DevOps设计</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>中级开发人员</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="E22" s="95">
-        <x:v>46264</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="F22" s="95">
-        <x:v>46269</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="G22" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6233,7 +6228,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J22" s="9">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10" ht="34" customHeight="1">
@@ -6241,19 +6236,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>T029</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>验证水印、权限控制、归档和大文件性能</x:v>
+        <x:v>编制CA、电子文档、BI报表POC方案与评分标准</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E23" s="95">
-        <x:v>46270</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="F23" s="95">
-        <x:v>46274</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="G23" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6265,7 +6260,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J23" s="9">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10" ht="34" customHeight="1">
@@ -6273,19 +6268,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>T030</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>验证数据接入、指标模型和经营报表</x:v>
+        <x:v>验证证书签发、身份认证和证书管理</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
         <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="E24" s="95">
-        <x:v>46275</x:v>
+        <x:v>46254</x:v>
       </x:c>
       <x:c r="F24" s="95">
-        <x:v>46279</x:v>
+        <x:v>46258</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6297,7 +6292,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J24" s="9">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10" ht="34" customHeight="1">
@@ -6305,19 +6300,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>T031</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>验证权限、钻取、导出和查询性能</x:v>
+        <x:v>验证电子签名、验签、时间戳和审计追溯</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="E25" s="95">
-        <x:v>46280</x:v>
+        <x:v>46259</x:v>
       </x:c>
       <x:c r="F25" s="95">
-        <x:v>46284</x:v>
+        <x:v>46263</x:v>
       </x:c>
       <x:c r="G25" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6329,135 +6324,135 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J25" s="9">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10" ht="34" customHeight="1">
       <x:c r="A26" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v/>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v/>
+        <x:v>验证模板生成、在线预览和格式转换</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E26" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F26" s="95" t="str">
-        <x:v/>
+        <x:v>中级开发人员</x:v>
+      </x:c>
+      <x:c r="E26" s="95">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="F26" s="95">
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H26" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I26" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J26" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J26" s="9">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10" ht="34" customHeight="1">
       <x:c r="A27" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v/>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v/>
+        <x:v>验证水印、权限控制、归档和大文件性能</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E27" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F27" s="95" t="str">
-        <x:v/>
+        <x:v>高级测试人员、中级测试人员</x:v>
+      </x:c>
+      <x:c r="E27" s="95">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="F27" s="95">
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="G27" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H27" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J27" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J27" s="9">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10" ht="34" customHeight="1">
       <x:c r="A28" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v/>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v/>
+        <x:v>验证数据接入、指标模型和经营报表</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E28" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F28" s="95" t="str">
-        <x:v/>
+        <x:v>高级开发人员</x:v>
+      </x:c>
+      <x:c r="E28" s="95">
+        <x:v>46275</x:v>
+      </x:c>
+      <x:c r="F28" s="95">
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="G28" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H28" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I28" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J28" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J28" s="9">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10" ht="34" customHeight="1">
       <x:c r="A29" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v/>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v/>
+        <x:v>验证权限、钻取、导出和查询性能</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E29" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F29" s="95" t="str">
-        <x:v/>
+        <x:v>高级测试人员、中级测试人员</x:v>
+      </x:c>
+      <x:c r="E29" s="95">
+        <x:v>46280</x:v>
+      </x:c>
+      <x:c r="F29" s="95">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="G29" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H29" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I29" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J29" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J29" s="9">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10" ht="34" customHeight="1">
@@ -9542,7 +9537,7 @@
         <x:v>46147</x:v>
       </x:c>
       <x:c r="H5" s="9">
-        <x:v>-141</x:v>
+        <x:v>-142</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9579,7 +9574,7 @@
         <x:v>46175</x:v>
       </x:c>
       <x:c r="H6" s="9">
-        <x:v>-113</x:v>
+        <x:v>-114</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9616,7 +9611,7 @@
         <x:v>46203</x:v>
       </x:c>
       <x:c r="H7" s="9">
-        <x:v>-85</x:v>
+        <x:v>-86</x:v>
       </x:c>
       <x:c r="I7" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9653,7 +9648,7 @@
         <x:v>46215</x:v>
       </x:c>
       <x:c r="H8" s="9">
-        <x:v>-73</x:v>
+        <x:v>-74</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9690,7 +9685,7 @@
         <x:v>46218</x:v>
       </x:c>
       <x:c r="H9" s="9">
-        <x:v>-70</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="I9" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9727,7 +9722,7 @@
         <x:v>46227</x:v>
       </x:c>
       <x:c r="H10" s="9">
-        <x:v>-61</x:v>
+        <x:v>-62</x:v>
       </x:c>
       <x:c r="I10" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9764,7 +9759,7 @@
         <x:v>46233</x:v>
       </x:c>
       <x:c r="H11" s="9">
-        <x:v>-55</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="I11" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9801,7 +9796,7 @@
         <x:v>46240</x:v>
       </x:c>
       <x:c r="H12" s="9">
-        <x:v>-48</x:v>
+        <x:v>-49</x:v>
       </x:c>
       <x:c r="I12" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9838,7 +9833,7 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="H13" s="9">
-        <x:v>-39</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="I13" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9869,13 +9864,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G14" s="95">
         <x:v>46252</x:v>
       </x:c>
       <x:c r="H14" s="9">
-        <x:v>-36</x:v>
+        <x:v>-37</x:v>
       </x:c>
       <x:c r="I14" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9912,7 +9907,7 @@
         <x:v>46253</x:v>
       </x:c>
       <x:c r="H15" s="9">
-        <x:v>-35</x:v>
+        <x:v>-36</x:v>
       </x:c>
       <x:c r="I15" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9949,7 +9944,7 @@
         <x:v>46258</x:v>
       </x:c>
       <x:c r="H16" s="9">
-        <x:v>-30</x:v>
+        <x:v>-31</x:v>
       </x:c>
       <x:c r="I16" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9980,13 +9975,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F17" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G17" s="95">
         <x:v>46263</x:v>
       </x:c>
       <x:c r="H17" s="9">
-        <x:v>-25</x:v>
+        <x:v>-26</x:v>
       </x:c>
       <x:c r="I17" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10023,7 +10018,7 @@
         <x:v>46264</x:v>
       </x:c>
       <x:c r="H18" s="9">
-        <x:v>-24</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="I18" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10060,7 +10055,7 @@
         <x:v>46265</x:v>
       </x:c>
       <x:c r="H19" s="9">
-        <x:v>-23</x:v>
+        <x:v>-24</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10097,7 +10092,7 @@
         <x:v>46269</x:v>
       </x:c>
       <x:c r="H20" s="9">
-        <x:v>-19</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="I20" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10128,13 +10123,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G21" s="95">
         <x:v>46274</x:v>
       </x:c>
       <x:c r="H21" s="9">
-        <x:v>-14</x:v>
+        <x:v>-15</x:v>
       </x:c>
       <x:c r="I21" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10171,7 +10166,7 @@
         <x:v>46279</x:v>
       </x:c>
       <x:c r="H22" s="9">
-        <x:v>-9</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="I22" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10208,7 +10203,7 @@
         <x:v>46279</x:v>
       </x:c>
       <x:c r="H23" s="9">
-        <x:v>-9</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="I23" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10245,7 +10240,7 @@
         <x:v>46283</x:v>
       </x:c>
       <x:c r="H24" s="9">
-        <x:v>-5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="I24" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10276,13 +10271,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="F25" s="9" t="str">
-        <x:v>测试人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G25" s="95">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="H25" s="9">
-        <x:v>-4</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="I25" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10319,7 +10314,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="H26" s="9">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I26" s="9" t="str">
         <x:v>临近到期</x:v>
@@ -10356,7 +10351,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="H27" s="9">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
         <x:v>正常</x:v>
@@ -10393,7 +10388,7 @@
         <x:v>46297</x:v>
       </x:c>
       <x:c r="H28" s="9">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I28" s="9" t="str">
         <x:v>正常</x:v>
@@ -10430,7 +10425,7 @@
         <x:v>46300</x:v>
       </x:c>
       <x:c r="H29" s="9">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I29" s="9" t="str">
         <x:v>正常</x:v>
@@ -10446,37 +10441,37 @@
     </x:row>
     <x:row r="30" spans="1:13" ht="34" customHeight="1">
       <x:c r="A30" s="9" t="str">
-        <x:v/>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v/>
+        <x:v>T035</x:v>
       </x:c>
       <x:c r="C30" s="102" t="str">
-        <x:v/>
+        <x:v>建立项目组织、RACI与沟通机制</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v/>
+        <x:v>MS006</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v/>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F30" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="G30" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H30" s="9" t="str">
-        <x:v/>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="G30" s="95">
+        <x:v>46303</x:v>
+      </x:c>
+      <x:c r="H30" s="9">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="9" t="str">
-        <x:v/>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="J30" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K30" s="102" t="str">
-        <x:v/>
+        <x:v>按计划提交可验收证据</x:v>
       </x:c>
       <x:c r="L30" s="10"/>
       <x:c r="M30" s="102"/>
@@ -12480,7 +12475,7 @@
     <x:row r="2" spans="1:10" ht="20" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:f>"数据截止"&amp;_数据接口!B5&amp;"。面向项目领导，重点呈现状态、风险、决策和未来两周行动。"</x:f>
-        <x:v>数据截止2026-09-23。面向项目领导，重点呈现状态、风险、决策和未来两周行动。</x:v>
+        <x:v>数据截止2026-09-24。面向项目领导，重点呈现状态、风险、决策和未来两周行动。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -12496,7 +12491,7 @@
       <x:c r="A3" s="7"/>
       <x:c r="B3" s="7" t="str">
         <x:f>'_数据接口'!B5</x:f>
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C3" s="7"/>
       <x:c r="D3" s="19"/>
@@ -12851,7 +12846,7 @@
       </x:c>
       <x:c r="B29" s="46">
         <x:f>IF('_数据接口'!B11=0,0,'_数据接口'!B22/'_数据接口'!B11)</x:f>
-        <x:v>0.0666666666666667</x:v>
+        <x:v>0.06666666666666667</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
         <x:v>294</x:v>
@@ -13512,16 +13507,36 @@
       <x:c r="L13" s="12"/>
     </x:row>
     <x:row r="14" spans="1:12" ht="20" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="11"/>
-      <x:c r="C14" s="7"/>
-      <x:c r="D14" s="12"/>
-      <x:c r="E14" s="7"/>
-      <x:c r="F14" s="7"/>
-      <x:c r="G14" s="7"/>
-      <x:c r="H14" s="7"/>
-      <x:c r="I14" s="7"/>
-      <x:c r="J14" s="7"/>
+      <x:c r="A14" s="7" t="str">
+        <x:v>RUN-20260924-001</x:v>
+      </x:c>
+      <x:c r="B14" s="97">
+        <x:v>46289.45585648148</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="str">
+        <x:v>全量刷新与质检</x:v>
+      </x:c>
+      <x:c r="D14" s="96">
+        <x:v>46289</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>里程碑、总控、门禁、风险、决策、相关方及模块完整性</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="str">
+        <x:v>发现25项数据质量问题，其中4项阻断、21项需整改；19项任务已延期</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="str">
+        <x:v>优先处理阻断项，并由任务负责人补齐逾期任务的实际状态、日期和完成证据</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="str">
+        <x:v>待项目经理确认</x:v>
+      </x:c>
+      <x:c r="J14" s="7" t="str">
+        <x:v>项目经理</x:v>
+      </x:c>
       <x:c r="K14" s="7"/>
       <x:c r="L14" s="12"/>
     </x:row>
@@ -14861,7 +14876,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2" ht="22" customHeight="1">
@@ -14941,7 +14956,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -14957,7 +14972,7 @@
         <x:v>计划人天</x:v>
       </x:c>
       <x:c r="B17" s="92">
-        <x:v>5433</x:v>
+        <x:v>4973</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -14965,7 +14980,7 @@
         <x:v>计划人工成本</x:v>
       </x:c>
       <x:c r="B18" s="93">
-        <x:v>7697700</x:v>
+        <x:v>6924600</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -14973,7 +14988,7 @@
         <x:v>平均人日单价</x:v>
       </x:c>
       <x:c r="B19" s="94">
-        <x:v>1416.8415240198785</x:v>
+        <x:v>1392.4391715262418</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -14981,7 +14996,7 @@
         <x:v>成本数据日期</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -15045,7 +15060,7 @@
         <x:v>14天内到期</x:v>
       </x:c>
       <x:c r="B28">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -15132,17 +15147,11 @@
       <x:c r="A39" t="str">
         <x:v>迁移来源线索数</x:v>
       </x:c>
-      <x:c r="B39">
-        <x:v>6</x:v>
-      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
         <x:v>已盘点来源系统数</x:v>
       </x:c>
-      <x:c r="B40">
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
@@ -15155,9 +15164,6 @@
     <x:row r="42">
       <x:c r="A42" t="str">
         <x:v>迁移门禁数</x:v>
-      </x:c>
-      <x:c r="B42">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -14972,7 +14972,7 @@
         <x:v>计划人天</x:v>
       </x:c>
       <x:c r="B17" s="92">
-        <x:v>4973</x:v>
+        <x:v>4721</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -14980,7 +14980,7 @@
         <x:v>计划人工成本</x:v>
       </x:c>
       <x:c r="B18" s="93">
-        <x:v>6924600</x:v>
+        <x:v>6525700</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -14988,7 +14988,7 @@
         <x:v>平均人日单价</x:v>
       </x:c>
       <x:c r="B19" s="94">
-        <x:v>1392.4391715262418</x:v>
+        <x:v>1382.270705359034</x:v>
       </x:c>
     </x:row>
     <x:row r="20">

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -4182,12 +4182,15 @@
       </x:c>
       <x:c r="B9" s="65">
         <x:f>'_数据接口'!B17</x:f>
+        <x:v>4721</x:v>
       </x:c>
       <x:c r="C9" s="89">
         <x:f>'_数据接口'!B18</x:f>
+        <x:v>6525700</x:v>
       </x:c>
       <x:c r="D9" s="90">
         <x:f>'_数据接口'!B19</x:f>
+        <x:v>1382.27070535903</x:v>
       </x:c>
       <x:c r="E9" s="20">
         <x:f>'_数据接口'!B29</x:f>

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -4182,15 +4182,12 @@
       </x:c>
       <x:c r="B9" s="65">
         <x:f>'_数据接口'!B17</x:f>
-        <x:v>4721</x:v>
       </x:c>
       <x:c r="C9" s="89">
         <x:f>'_数据接口'!B18</x:f>
-        <x:v>6525700</x:v>
       </x:c>
       <x:c r="D9" s="90">
         <x:f>'_数据接口'!B19</x:f>
-        <x:v>1382.27070535903</x:v>
       </x:c>
       <x:c r="E9" s="20">
         <x:f>'_数据接口'!B29</x:f>
@@ -14975,7 +14972,7 @@
         <x:v>计划人天</x:v>
       </x:c>
       <x:c r="B17" s="92">
-        <x:v>4721</x:v>
+        <x:v>4337</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -14983,7 +14980,7 @@
         <x:v>计划人工成本</x:v>
       </x:c>
       <x:c r="B18" s="93">
-        <x:v>6525700</x:v>
+        <x:v>6070900</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -14991,7 +14988,7 @@
         <x:v>平均人日单价</x:v>
       </x:c>
       <x:c r="B19" s="94">
-        <x:v>1382.270705359034</x:v>
+        <x:v>1399.7924832833755</x:v>
       </x:c>
     </x:row>
     <x:row r="20">

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -1931,7 +1931,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="105">
+  <x:cellXfs count="106">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2238,6 +2238,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -4168,7 +4171,9 @@
       <x:c r="H8" s="61" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="I8" s="5"/>
+      <x:c r="I8" s="60" t="str">
+        <x:v>已量化总预算</x:v>
+      </x:c>
       <x:c r="J8" s="63"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="5"/>
@@ -4182,12 +4187,15 @@
       </x:c>
       <x:c r="B9" s="65">
         <x:f>'_数据接口'!B17</x:f>
+        <x:v>4337</x:v>
       </x:c>
       <x:c r="C9" s="89">
         <x:f>'_数据接口'!B18</x:f>
+        <x:v>6070900</x:v>
       </x:c>
       <x:c r="D9" s="90">
         <x:f>'_数据接口'!B19</x:f>
+        <x:v>1399.79248328338</x:v>
       </x:c>
       <x:c r="E9" s="20">
         <x:f>'_数据接口'!B29</x:f>
@@ -4205,7 +4213,10 @@
         <x:f>'_数据接口'!B32</x:f>
         <x:v>34</x:v>
       </x:c>
-      <x:c r="I9" s="2"/>
+      <x:c r="I9" s="89">
+        <x:f>'_数据接口'!B43</x:f>
+        <x:v>15252170</x:v>
+      </x:c>
       <x:c r="J9" s="2"/>
       <x:c r="K9" s="2"/>
       <x:c r="L9" s="2"/>
@@ -14832,7 +14843,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr/>
-  <x:dimension ref="A1:B42"/>
+  <x:dimension ref="A1:B43"/>
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <x:cols>
     <x:col min="1" max="1" width="20" customWidth="1"/>
@@ -15166,6 +15177,14 @@
         <x:v>迁移门禁数</x:v>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>已量化总预算</x:v>
+      </x:c>
+      <x:c r="B43">
+        <x:v>15252170</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter/>

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -1931,7 +1931,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="106">
+  <x:cellXfs count="107">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2241,6 +2241,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="2" fillId="3" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -2627,19 +2630,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>122</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3997,7 +4000,7 @@
         <x:v>统计日期</x:v>
       </x:c>
       <x:c r="B3" s="91">
-        <x:v>46289</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="C3" s="2"/>
       <x:c r="D3" s="2"/>
@@ -4079,15 +4082,12 @@
       </x:c>
       <x:c r="B6" s="57">
         <x:f>'_数据接口'!B22</x:f>
-        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="57">
         <x:f>'_数据接口'!B23</x:f>
-        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="57">
         <x:f>'_数据接口'!B24</x:f>
-        <x:v>122</x:v>
       </x:c>
       <x:c r="E6" s="57">
         <x:f>'_数据接口'!B25</x:f>
@@ -4095,11 +4095,9 @@
       </x:c>
       <x:c r="F6" s="58">
         <x:f>'_数据接口'!B26</x:f>
-        <x:v>0.025925925925925925</x:v>
       </x:c>
       <x:c r="G6" s="57">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>19</x:v>
       </x:c>
       <x:c r="H6" s="57">
         <x:f>'_数据接口'!B28</x:f>
@@ -4174,16 +4172,25 @@
       <x:c r="I8" s="60" t="str">
         <x:v>已量化总预算</x:v>
       </x:c>
-      <x:c r="J8" s="63"/>
-      <x:c r="K8" s="4"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="63"/>
-      <x:c r="N8" s="5"/>
+      <x:c r="J8" s="63" t="str">
+        <x:v>迭代承诺完成率</x:v>
+      </x:c>
+      <x:c r="K8" s="4" t="str">
+        <x:v>迭代负载率</x:v>
+      </x:c>
+      <x:c r="L8" s="5" t="str">
+        <x:v>预测超基线任务</x:v>
+      </x:c>
+      <x:c r="M8" s="63" t="str">
+        <x:v>平均偏差天数</x:v>
+      </x:c>
+      <x:c r="N8" s="5" t="str">
+        <x:v>当前迭代周</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:14" ht="26" customHeight="1">
       <x:c r="A9" s="64">
         <x:f>'_数据接口'!B26</x:f>
-        <x:v>0.025925925925925925</x:v>
       </x:c>
       <x:c r="B9" s="65">
         <x:f>'_数据接口'!B17</x:f>
@@ -4217,11 +4224,25 @@
         <x:f>'_数据接口'!B43</x:f>
         <x:v>15252170</x:v>
       </x:c>
-      <x:c r="J9" s="2"/>
-      <x:c r="K9" s="2"/>
-      <x:c r="L9" s="2"/>
-      <x:c r="M9" s="2"/>
-      <x:c r="N9" s="2"/>
+      <x:c r="J9" s="106">
+        <x:f>'_数据接口'!B44</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="K9" s="106">
+        <x:f>'_数据接口'!B45</x:f>
+        <x:v>1.3333</x:v>
+      </x:c>
+      <x:c r="L9" s="2">
+        <x:f>'_数据接口'!B46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="2">
+        <x:f>'_数据接口'!B47</x:f>
+      </x:c>
+      <x:c r="N9" s="2" t="str">
+        <x:f>'_数据接口'!B48</x:f>
+        <x:v>2026-W40</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:14" ht="20" customHeight="1">
       <x:c r="A10" s="7"/>
@@ -4283,7 +4304,6 @@
       </x:c>
       <x:c r="B12" s="7">
         <x:f>'_数据接口'!B22</x:f>
-        <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
         <x:v>83</x:v>
@@ -4323,7 +4343,6 @@
       </x:c>
       <x:c r="B13" s="7">
         <x:f>'_数据接口'!B23</x:f>
-        <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
         <x:v>90</x:v>
@@ -4363,7 +4382,6 @@
       </x:c>
       <x:c r="B14" s="2">
         <x:f>'_数据接口'!B24</x:f>
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
         <x:v>98</x:v>
@@ -4442,7 +4460,6 @@
       </x:c>
       <x:c r="B16" s="4">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
         <x:v>108</x:v>
@@ -4542,7 +4559,6 @@
       </x:c>
       <x:c r="J19" s="2">
         <x:f>'_数据接口'!B40</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="K19" s="2" t="str">
         <x:f>'_数据接口'!B41</x:f>
@@ -5000,7 +5016,7 @@
     <x:row r="2" spans="1:12" ht="20" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:f>"数据截止"&amp;'_数据接口'!B5&amp;"。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。"</x:f>
-        <x:v>数据截止2026-09-24。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。</x:v>
+        <x:v>数据截止2026-10-16。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -5034,7 +5050,7 @@
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:f>'_数据接口'!B5</x:f>
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="7" t="s">
@@ -5106,11 +5122,11 @@
       </x:c>
       <x:c r="B7" s="5">
         <x:f>'_数据接口'!B22</x:f>
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="2">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="20">
         <x:f>'_数据接口'!B28</x:f>
@@ -5204,7 +5220,7 @@
       </x:c>
       <x:c r="C11" s="2" t="str">
         <x:f>'_数据接口'!B27&amp;"项任务已延期或计划完成日已过"</x:f>
-        <x:v>19项任务已延期或计划完成日已过</x:v>
+        <x:v>17项任务已延期或计划完成日已过</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
         <x:v>153</x:v>
@@ -5796,34 +5812,34 @@
     </x:row>
     <x:row r="9" spans="1:10" ht="34" customHeight="1">
       <x:c r="A9" s="9" t="str">
-        <x:v>项目总控台账</x:v>
+        <x:v>开发前检查清单-20261008-V1.xlsx</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>T008</x:v>
+        <x:v>MODULE-CODE</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>汇编可研报告并组织评审</x:v>
+        <x:v>模块编号检查</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
         <x:v>项目经理</x:v>
       </x:c>
-      <x:c r="E9" s="95">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F9" s="95">
-        <x:v>46283</x:v>
+      <x:c r="E9" s="95" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F9" s="95" t="str">
+        <x:v/>
       </x:c>
       <x:c r="G9" s="9" t="str">
-        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
+        <x:v>缺少_data接口工作表</x:v>
       </x:c>
       <x:c r="H9" s="9" t="str">
-        <x:v>需整改</x:v>
+        <x:v>阻断</x:v>
       </x:c>
       <x:c r="I9" s="9" t="str">
-        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
-      </x:c>
-      <x:c r="J9" s="9">
-        <x:v>11</x:v>
+        <x:v>补充_data接口并填写模块编号</x:v>
+      </x:c>
+      <x:c r="J9" s="9" t="str">
+        <x:v>-</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10" ht="34" customHeight="1">
@@ -5863,19 +5879,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>T012</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>访谈业务部门并形成痛点清单</x:v>
+        <x:v>制定项目治理、会议与报告机制</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="E11" s="95">
-        <x:v>46148</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="F11" s="95">
-        <x:v>46175</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5887,7 +5903,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J11" s="9">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10" ht="34" customHeight="1">
@@ -5895,19 +5911,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>T013</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>确认现状流程、问题与改进机会基线</x:v>
+        <x:v>制定需求分级、跟踪与变更规范</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="E12" s="95">
-        <x:v>46176</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="F12" s="95">
-        <x:v>46203</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5919,7 +5935,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J12" s="9">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10" ht="34" customHeight="1">
@@ -5927,19 +5943,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>T014</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>制定项目治理、会议与报告机制</x:v>
+        <x:v>制定设计、编码与代码评审规范</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E13" s="95">
-        <x:v>46204</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="F13" s="95">
-        <x:v>46215</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5951,7 +5967,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J13" s="9">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10" ht="34" customHeight="1">
@@ -5959,19 +5975,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>T015</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>制定需求分级、跟踪与变更规范</x:v>
+        <x:v>制定测试、缺陷与质量门禁规范</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="E14" s="95">
-        <x:v>46216</x:v>
+        <x:v>46241</x:v>
       </x:c>
       <x:c r="F14" s="95">
-        <x:v>46227</x:v>
+        <x:v>46252</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -5983,7 +5999,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J14" s="9">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10" ht="34" customHeight="1">
@@ -5991,19 +6007,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>T016</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>制定设计、编码与代码评审规范</x:v>
+        <x:v>制定配置、发布与文档归档规范</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="E15" s="95">
-        <x:v>46228</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="F15" s="95">
-        <x:v>46240</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="G15" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6015,7 +6031,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J15" s="9">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10" ht="34" customHeight="1">
@@ -6023,19 +6039,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>T017</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>制定测试、缺陷与质量门禁规范</x:v>
+        <x:v>完成系统分层、模块与服务边界设计</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E16" s="95">
-        <x:v>46241</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="F16" s="95">
-        <x:v>46252</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="G16" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6047,7 +6063,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J16" s="9">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10" ht="34" customHeight="1">
@@ -6055,19 +6071,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>T018</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>制定配置、发布与文档归档规范</x:v>
+        <x:v>完成主数据、交易数据与分析数据架构</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E17" s="95">
-        <x:v>46253</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="F17" s="95">
-        <x:v>46265</x:v>
+        <x:v>46233</x:v>
       </x:c>
       <x:c r="G17" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6079,7 +6095,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J17" s="9">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10" ht="34" customHeight="1">
@@ -6087,19 +6103,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>T019</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>完成系统分层、模块与服务边界设计</x:v>
+        <x:v>完成内部及外部接口总体架构</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="E18" s="95">
-        <x:v>46204</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="F18" s="95">
-        <x:v>46218</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6111,7 +6127,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J18" s="9">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10" ht="34" customHeight="1">
@@ -6119,19 +6135,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>T020</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>完成主数据、交易数据与分析数据架构</x:v>
+        <x:v>完成身份、权限、审计与数据安全设计</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
         <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E19" s="95">
-        <x:v>46219</x:v>
+        <x:v>46250</x:v>
       </x:c>
       <x:c r="F19" s="95">
-        <x:v>46233</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6143,7 +6159,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J19" s="9">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10" ht="34" customHeight="1">
@@ -6151,19 +6167,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>T021</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>完成内部及外部接口总体架构</x:v>
+        <x:v>完成环境、网络、容灾和DevOps设计</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="E20" s="95">
-        <x:v>46234</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="F20" s="95">
-        <x:v>46249</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6175,7 +6191,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J20" s="9">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="34" customHeight="1">
@@ -6183,19 +6199,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>T022</x:v>
+        <x:v>T024</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>完成身份、权限、审计与数据安全设计</x:v>
+        <x:v>汇编总体技术架构并完成基线评审</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
         <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E21" s="95">
-        <x:v>46250</x:v>
+        <x:v>46280</x:v>
       </x:c>
       <x:c r="F21" s="95">
-        <x:v>46264</x:v>
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6207,7 +6223,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J21" s="9">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10" ht="34" customHeight="1">
@@ -6215,19 +6231,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>T023</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>完成环境、网络、容灾和DevOps设计</x:v>
+        <x:v>编制CA、电子文档、BI报表POC方案与评分标准</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="E22" s="95">
-        <x:v>46265</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="F22" s="95">
-        <x:v>46279</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="G22" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6239,7 +6255,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J22" s="9">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10" ht="34" customHeight="1">
@@ -6247,19 +6263,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>T025</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>编制CA、电子文档、BI报表POC方案与评分标准</x:v>
+        <x:v>验证证书签发、身份认证和证书管理</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="E23" s="95">
-        <x:v>46249</x:v>
+        <x:v>46254</x:v>
       </x:c>
       <x:c r="F23" s="95">
-        <x:v>46253</x:v>
+        <x:v>46258</x:v>
       </x:c>
       <x:c r="G23" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6271,7 +6287,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J23" s="9">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10" ht="34" customHeight="1">
@@ -6279,19 +6295,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>T026</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>验证证书签发、身份认证和证书管理</x:v>
+        <x:v>验证电子签名、验签、时间戳和审计追溯</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="E24" s="95">
-        <x:v>46254</x:v>
+        <x:v>46259</x:v>
       </x:c>
       <x:c r="F24" s="95">
-        <x:v>46258</x:v>
+        <x:v>46263</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6303,7 +6319,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J24" s="9">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10" ht="34" customHeight="1">
@@ -6311,19 +6327,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>T027</x:v>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>验证电子签名、验签、时间戳和审计追溯</x:v>
+        <x:v>验证模板生成、在线预览和格式转换</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>中级开发人员</x:v>
       </x:c>
       <x:c r="E25" s="95">
-        <x:v>46259</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="F25" s="95">
-        <x:v>46263</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="G25" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6335,7 +6351,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J25" s="9">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10" ht="34" customHeight="1">
@@ -6343,19 +6359,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>T028</x:v>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>验证模板生成、在线预览和格式转换</x:v>
+        <x:v>验证水印、权限控制、归档和大文件性能</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>中级开发人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="E26" s="95">
-        <x:v>46264</x:v>
+        <x:v>46270</x:v>
       </x:c>
       <x:c r="F26" s="95">
-        <x:v>46269</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6367,7 +6383,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J26" s="9">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10" ht="34" customHeight="1">
@@ -6375,19 +6391,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>T029</x:v>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>验证水印、权限控制、归档和大文件性能</x:v>
+        <x:v>验证数据接入、指标模型和经营报表</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="E27" s="95">
-        <x:v>46270</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="F27" s="95">
-        <x:v>46274</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="G27" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6399,7 +6415,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J27" s="9">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10" ht="34" customHeight="1">
@@ -6407,19 +6423,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>T030</x:v>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>验证数据接入、指标模型和经营报表</x:v>
+        <x:v>验证权限、钻取、导出和查询性能</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="E28" s="95">
-        <x:v>46275</x:v>
+        <x:v>46280</x:v>
       </x:c>
       <x:c r="F28" s="95">
-        <x:v>46279</x:v>
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="G28" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6431,7 +6447,7 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J28" s="9">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10" ht="34" customHeight="1">
@@ -6439,19 +6455,19 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>T031</x:v>
+        <x:v>T032</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>验证权限、钻取、导出和查询性能</x:v>
+        <x:v>汇总问题清单、适配结论和产品选型建议</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="E29" s="95">
-        <x:v>46280</x:v>
+        <x:v>46285</x:v>
       </x:c>
       <x:c r="F29" s="95">
-        <x:v>46284</x:v>
+        <x:v>46290</x:v>
       </x:c>
       <x:c r="G29" s="9" t="str">
         <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
@@ -6463,167 +6479,167 @@
         <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
       </x:c>
       <x:c r="J29" s="9">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10" ht="34" customHeight="1">
       <x:c r="A30" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v/>
+        <x:v>T033</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v/>
+        <x:v>编制并审批项目章程</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E30" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F30" s="95" t="str">
-        <x:v/>
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="E30" s="95">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="F30" s="95">
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="G30" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H30" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I30" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J30" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J30" s="9">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10" ht="34" customHeight="1">
       <x:c r="A31" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v/>
+        <x:v>T034</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v/>
+        <x:v>编制范围、里程碑和主进度计划</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E31" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F31" s="95" t="str">
-        <x:v/>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="E31" s="95">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="F31" s="95">
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H31" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I31" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J31" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J31" s="9">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10" ht="34" customHeight="1">
       <x:c r="A32" s="9" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v/>
+        <x:v>T035</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v/>
+        <x:v>建立项目组织、RACI与沟通机制</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E32" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F32" s="95" t="str">
-        <x:v/>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="E32" s="95">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="F32" s="95">
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H32" s="9" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I32" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J32" s="9" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J32" s="9">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10" ht="20" customHeight="1">
       <x:c r="A33" s="7" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
-        <x:v/>
+        <x:v>T036</x:v>
       </x:c>
       <x:c r="C33" s="7" t="str">
-        <x:v/>
+        <x:v>确认30人团队投入与阶段资源计划</x:v>
       </x:c>
       <x:c r="D33" s="7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E33" s="96" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F33" s="96" t="str">
-        <x:v/>
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="E33" s="96">
+        <x:v>46304</x:v>
+      </x:c>
+      <x:c r="F33" s="96">
+        <x:v>46305</x:v>
       </x:c>
       <x:c r="G33" s="7" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H33" s="7" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I33" s="7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J33" s="7" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J33" s="7">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10" ht="20" customHeight="1">
       <x:c r="A34" s="7" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B34" s="7" t="str">
-        <x:v/>
+        <x:v>T037</x:v>
       </x:c>
       <x:c r="C34" s="7" t="str">
-        <x:v/>
+        <x:v>建立风险、问题、变更和决策台账</x:v>
       </x:c>
       <x:c r="D34" s="7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E34" s="96" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F34" s="96" t="str">
-        <x:v/>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="E34" s="96">
+        <x:v>46306</x:v>
+      </x:c>
+      <x:c r="F34" s="96">
+        <x:v>46308</x:v>
       </x:c>
       <x:c r="G34" s="7" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H34" s="7" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I34" s="7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J34" s="7" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J34" s="7">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10" ht="20" customHeight="1">
@@ -9548,7 +9564,7 @@
         <x:v>46147</x:v>
       </x:c>
       <x:c r="H5" s="9">
-        <x:v>-142</x:v>
+        <x:v>-164</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9567,25 +9583,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>T012</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="C6" s="102" t="str">
-        <x:v>访谈业务部门并形成痛点清单</x:v>
+        <x:v>制定项目治理、会议与报告机制</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>MS003</x:v>
+        <x:v>MS004</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="G6" s="95">
-        <x:v>46175</x:v>
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="H6" s="9">
-        <x:v>-114</x:v>
+        <x:v>-96</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9604,25 +9620,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>T013</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="C7" s="102" t="str">
-        <x:v>确认现状流程、问题与改进机会基线</x:v>
+        <x:v>完成系统分层、模块与服务边界设计</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>MS003</x:v>
+        <x:v>MS005</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="G7" s="95">
-        <x:v>46203</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="H7" s="9">
-        <x:v>-86</x:v>
+        <x:v>-93</x:v>
       </x:c>
       <x:c r="I7" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9641,10 +9657,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>T014</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="C8" s="102" t="str">
-        <x:v>制定项目治理、会议与报告机制</x:v>
+        <x:v>制定需求分级、跟踪与变更规范</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
         <x:v>MS004</x:v>
@@ -9653,13 +9669,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="G8" s="95">
-        <x:v>46215</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="H8" s="9">
-        <x:v>-74</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9678,10 +9694,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>T019</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="C9" s="102" t="str">
-        <x:v>完成系统分层、模块与服务边界设计</x:v>
+        <x:v>完成主数据、交易数据与分析数据架构</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
         <x:v>MS005</x:v>
@@ -9693,10 +9709,10 @@
         <x:v>技术经理</x:v>
       </x:c>
       <x:c r="G9" s="95">
-        <x:v>46218</x:v>
+        <x:v>46233</x:v>
       </x:c>
       <x:c r="H9" s="9">
-        <x:v>-71</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="I9" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9715,10 +9731,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>T015</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="C10" s="102" t="str">
-        <x:v>制定需求分级、跟踪与变更规范</x:v>
+        <x:v>制定设计、编码与代码评审规范</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
         <x:v>MS004</x:v>
@@ -9727,13 +9743,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="G10" s="95">
-        <x:v>46227</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="H10" s="9">
-        <x:v>-62</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="I10" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9752,10 +9768,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>T020</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="C11" s="102" t="str">
-        <x:v>完成主数据、交易数据与分析数据架构</x:v>
+        <x:v>完成内部及外部接口总体架构</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
         <x:v>MS005</x:v>
@@ -9764,13 +9780,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="G11" s="95">
-        <x:v>46233</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="H11" s="9">
-        <x:v>-56</x:v>
+        <x:v>-62</x:v>
       </x:c>
       <x:c r="I11" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9789,10 +9805,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>T016</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="C12" s="102" t="str">
-        <x:v>制定设计、编码与代码评审规范</x:v>
+        <x:v>制定测试、缺陷与质量门禁规范</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>MS004</x:v>
@@ -9801,13 +9817,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G12" s="95">
-        <x:v>46240</x:v>
+        <x:v>46252</x:v>
       </x:c>
       <x:c r="H12" s="9">
-        <x:v>-49</x:v>
+        <x:v>-59</x:v>
       </x:c>
       <x:c r="I12" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9826,25 +9842,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>T021</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="C13" s="102" t="str">
-        <x:v>完成内部及外部接口总体架构</x:v>
+        <x:v>编制CA、电子文档、BI报表POC方案与评分标准</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>MS005</x:v>
+        <x:v>MS017</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="G13" s="95">
-        <x:v>46249</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="H13" s="9">
-        <x:v>-40</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I13" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9863,25 +9879,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>T017</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="C14" s="102" t="str">
-        <x:v>制定测试、缺陷与质量门禁规范</x:v>
+        <x:v>验证证书签发、身份认证和证书管理</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>MS004</x:v>
+        <x:v>MS017</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="G14" s="95">
-        <x:v>46252</x:v>
+        <x:v>46258</x:v>
       </x:c>
       <x:c r="H14" s="9">
-        <x:v>-37</x:v>
+        <x:v>-53</x:v>
       </x:c>
       <x:c r="I14" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9900,10 +9916,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>T025</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="C15" s="102" t="str">
-        <x:v>编制CA、电子文档、BI报表POC方案与评分标准</x:v>
+        <x:v>验证电子签名、验签、时间戳和审计追溯</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
         <x:v>MS017</x:v>
@@ -9912,13 +9928,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F15" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G15" s="95">
-        <x:v>46253</x:v>
+        <x:v>46263</x:v>
       </x:c>
       <x:c r="H15" s="9">
-        <x:v>-36</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="I15" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9937,25 +9953,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>T026</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="C16" s="102" t="str">
-        <x:v>验证证书签发、身份认证和证书管理</x:v>
+        <x:v>完成身份、权限、审计与数据安全设计</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>MS017</x:v>
+        <x:v>MS005</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="G16" s="95">
-        <x:v>46258</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="H16" s="9">
-        <x:v>-31</x:v>
+        <x:v>-47</x:v>
       </x:c>
       <x:c r="I16" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9974,25 +9990,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>T027</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="C17" s="102" t="str">
-        <x:v>验证电子签名、验签、时间戳和审计追溯</x:v>
+        <x:v>制定配置、发布与文档归档规范</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>MS017</x:v>
+        <x:v>MS004</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F17" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="G17" s="95">
-        <x:v>46263</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="H17" s="9">
-        <x:v>-26</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="I17" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10011,25 +10027,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>T022</x:v>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="C18" s="102" t="str">
-        <x:v>完成身份、权限、审计与数据安全设计</x:v>
+        <x:v>验证模板生成、在线预览和格式转换</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>MS005</x:v>
+        <x:v>MS017</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>中级开发人员</x:v>
       </x:c>
       <x:c r="G18" s="95">
-        <x:v>46264</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="H18" s="9">
-        <x:v>-25</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="I18" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10048,25 +10064,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>T018</x:v>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="C19" s="102" t="str">
-        <x:v>制定配置、发布与文档归档规范</x:v>
+        <x:v>验证水印、权限控制、归档和大文件性能</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>MS004</x:v>
+        <x:v>MS017</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G19" s="95">
-        <x:v>46265</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="H19" s="9">
-        <x:v>-24</x:v>
+        <x:v>-37</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10085,25 +10101,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>T028</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="C20" s="102" t="str">
-        <x:v>验证模板生成、在线预览和格式转换</x:v>
+        <x:v>完成环境、网络、容灾和DevOps设计</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>MS017</x:v>
+        <x:v>MS005</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>中级开发人员</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="G20" s="95">
-        <x:v>46269</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="H20" s="9">
-        <x:v>-20</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="I20" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10122,10 +10138,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>T029</x:v>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="C21" s="102" t="str">
-        <x:v>验证水印、权限控制、归档和大文件性能</x:v>
+        <x:v>验证数据接入、指标模型和经营报表</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
         <x:v>MS017</x:v>
@@ -10134,13 +10150,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="G21" s="95">
-        <x:v>46274</x:v>
+        <x:v>46279</x:v>
       </x:c>
       <x:c r="H21" s="9">
-        <x:v>-15</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="I21" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10159,25 +10175,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>T023</x:v>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="C22" s="102" t="str">
-        <x:v>完成环境、网络、容灾和DevOps设计</x:v>
+        <x:v>验证权限、钻取、导出和查询性能</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>MS005</x:v>
+        <x:v>MS017</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>待确认</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="G22" s="95">
-        <x:v>46279</x:v>
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="H22" s="9">
-        <x:v>-10</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I22" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10196,25 +10212,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>T030</x:v>
+        <x:v>T032</x:v>
       </x:c>
       <x:c r="C23" s="102" t="str">
-        <x:v>验证数据接入、指标模型和经营报表</x:v>
+        <x:v>汇总问题清单、适配结论和产品选型建议</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
         <x:v>MS017</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>待确认</x:v>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F23" s="9" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="G23" s="95">
-        <x:v>46279</x:v>
+        <x:v>46290</x:v>
       </x:c>
       <x:c r="H23" s="9">
-        <x:v>-10</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="I23" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10233,25 +10249,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>T008</x:v>
+        <x:v>T024</x:v>
       </x:c>
       <x:c r="C24" s="102" t="str">
-        <x:v>汇编可研报告并组织评审</x:v>
+        <x:v>汇编总体技术架构并完成基线评审</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>MS002</x:v>
+        <x:v>MS005</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="G24" s="95">
-        <x:v>46283</x:v>
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="H24" s="9">
-        <x:v>-6</x:v>
+        <x:v>-16</x:v>
       </x:c>
       <x:c r="I24" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10270,25 +10286,25 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>T031</x:v>
+        <x:v>T033</x:v>
       </x:c>
       <x:c r="C25" s="102" t="str">
-        <x:v>验证权限、钻取、导出和查询性能</x:v>
+        <x:v>编制并审批项目章程</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>MS017</x:v>
+        <x:v>MS006</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>进行中</x:v>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F25" s="9" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>项目集经理</x:v>
       </x:c>
       <x:c r="G25" s="95">
-        <x:v>46284</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="H25" s="9">
-        <x:v>-5</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="I25" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10307,13 +10323,13 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>T032</x:v>
+        <x:v>T034</x:v>
       </x:c>
       <x:c r="C26" s="102" t="str">
-        <x:v>汇总问题清单、适配结论和产品选型建议</x:v>
+        <x:v>编制范围、里程碑和主进度计划</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>MS017</x:v>
+        <x:v>MS006</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
         <x:v>未开始</x:v>
@@ -10322,19 +10338,19 @@
         <x:v>项目经理</x:v>
       </x:c>
       <x:c r="G26" s="95">
-        <x:v>46290</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="H26" s="9">
-        <x:v>1</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="I26" s="9" t="str">
-        <x:v>临近到期</x:v>
+        <x:v>已延期</x:v>
       </x:c>
       <x:c r="J26" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K26" s="102" t="str">
-        <x:v>按计划提交可验收证据</x:v>
+        <x:v>确认实际状态；完成、纠偏或提交基线变更</x:v>
       </x:c>
       <x:c r="L26" s="10"/>
       <x:c r="M26" s="102"/>
@@ -10344,34 +10360,34 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>T024</x:v>
+        <x:v>T035</x:v>
       </x:c>
       <x:c r="C27" s="102" t="str">
-        <x:v>汇编总体技术架构并完成基线评审</x:v>
+        <x:v>建立项目组织、RACI与沟通机制</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>MS005</x:v>
+        <x:v>MS006</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>进行中</x:v>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F27" s="9" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="G27" s="95">
-        <x:v>46295</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="H27" s="9">
-        <x:v>6</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>已延期</x:v>
       </x:c>
       <x:c r="J27" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K27" s="102" t="str">
-        <x:v>按计划提交可验收证据</x:v>
+        <x:v>确认实际状态；完成、纠偏或提交基线变更</x:v>
       </x:c>
       <x:c r="L27" s="10"/>
       <x:c r="M27" s="102"/>
@@ -10381,10 +10397,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>T033</x:v>
+        <x:v>T036</x:v>
       </x:c>
       <x:c r="C28" s="102" t="str">
-        <x:v>编制并审批项目章程</x:v>
+        <x:v>确认30人团队投入与阶段资源计划</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
         <x:v>MS006</x:v>
@@ -10396,19 +10412,19 @@
         <x:v>项目集经理</x:v>
       </x:c>
       <x:c r="G28" s="95">
-        <x:v>46297</x:v>
+        <x:v>46305</x:v>
       </x:c>
       <x:c r="H28" s="9">
-        <x:v>8</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="I28" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>已延期</x:v>
       </x:c>
       <x:c r="J28" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K28" s="102" t="str">
-        <x:v>按计划提交可验收证据</x:v>
+        <x:v>确认实际状态；完成、纠偏或提交基线变更</x:v>
       </x:c>
       <x:c r="L28" s="10"/>
       <x:c r="M28" s="102"/>
@@ -10418,10 +10434,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>T034</x:v>
+        <x:v>T037</x:v>
       </x:c>
       <x:c r="C29" s="102" t="str">
-        <x:v>编制范围、里程碑和主进度计划</x:v>
+        <x:v>建立风险、问题、变更和决策台账</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
         <x:v>MS006</x:v>
@@ -10433,19 +10449,19 @@
         <x:v>项目经理</x:v>
       </x:c>
       <x:c r="G29" s="95">
-        <x:v>46300</x:v>
+        <x:v>46308</x:v>
       </x:c>
       <x:c r="H29" s="9">
-        <x:v>11</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="I29" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>已延期</x:v>
       </x:c>
       <x:c r="J29" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K29" s="102" t="str">
-        <x:v>按计划提交可验收证据</x:v>
+        <x:v>确认实际状态；完成、纠偏或提交基线变更</x:v>
       </x:c>
       <x:c r="L29" s="10"/>
       <x:c r="M29" s="102"/>
@@ -10455,10 +10471,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>T035</x:v>
+        <x:v>T038</x:v>
       </x:c>
       <x:c r="C30" s="102" t="str">
-        <x:v>建立项目组织、RACI与沟通机制</x:v>
+        <x:v>完成启动条件检查与评审</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
         <x:v>MS006</x:v>
@@ -10467,16 +10483,16 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="F30" s="9" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>项目集经理</x:v>
       </x:c>
       <x:c r="G30" s="95">
-        <x:v>46303</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="H30" s="9">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I30" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>临近到期</x:v>
       </x:c>
       <x:c r="J30" s="102" t="str">
         <x:v/>
@@ -10489,148 +10505,148 @@
     </x:row>
     <x:row r="31" spans="1:13" ht="34" customHeight="1">
       <x:c r="A31" s="9" t="str">
-        <x:v/>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v/>
+        <x:v>T039</x:v>
       </x:c>
       <x:c r="C31" s="102" t="str">
-        <x:v/>
+        <x:v>准备启动会材料与项目目标宣贯</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v/>
+        <x:v>MS007</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v/>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="G31" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H31" s="9" t="str">
-        <x:v/>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="G31" s="95">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="H31" s="9">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I31" s="9" t="str">
-        <x:v/>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="J31" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K31" s="102" t="str">
-        <x:v/>
+        <x:v>按计划提交可验收证据</x:v>
       </x:c>
       <x:c r="L31" s="10"/>
       <x:c r="M31" s="102"/>
     </x:row>
     <x:row r="32" spans="1:13" ht="34" customHeight="1">
       <x:c r="A32" s="9" t="str">
-        <x:v/>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v/>
+        <x:v>T040</x:v>
       </x:c>
       <x:c r="C32" s="102" t="str">
-        <x:v/>
+        <x:v>召开项目启动会并确认职责</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v/>
+        <x:v>MS007</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v/>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="G32" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H32" s="9" t="str">
-        <x:v/>
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="G32" s="95">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="H32" s="9">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I32" s="9" t="str">
-        <x:v/>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="J32" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K32" s="102" t="str">
-        <x:v/>
+        <x:v>按计划提交可验收证据</x:v>
       </x:c>
       <x:c r="L32" s="10"/>
       <x:c r="M32" s="102"/>
     </x:row>
     <x:row r="33" spans="1:13" ht="34" customHeight="1">
       <x:c r="A33" s="9" t="str">
-        <x:v/>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v/>
+        <x:v>T041</x:v>
       </x:c>
       <x:c r="C33" s="102" t="str">
-        <x:v/>
+        <x:v>发布会议纪要、行动项和基准计划</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v/>
+        <x:v>MS007</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v/>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F33" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="G33" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H33" s="9" t="str">
-        <x:v/>
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="G33" s="95">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="H33" s="9">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I33" s="9" t="str">
-        <x:v/>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="J33" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K33" s="102" t="str">
-        <x:v/>
+        <x:v>按计划提交可验收证据</x:v>
       </x:c>
       <x:c r="L33" s="10"/>
       <x:c r="M33" s="102"/>
     </x:row>
     <x:row r="34" spans="1:13" ht="34" customHeight="1">
       <x:c r="A34" s="9" t="str">
-        <x:v/>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v/>
+        <x:v>T042</x:v>
       </x:c>
       <x:c r="C34" s="102" t="str">
-        <x:v/>
+        <x:v>开展业务场景与用户需求工作坊</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v/>
+        <x:v>MS008</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v/>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F34" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="G34" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H34" s="9" t="str">
-        <x:v/>
+        <x:v>产品经理</x:v>
+      </x:c>
+      <x:c r="G34" s="95">
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="H34" s="9">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I34" s="9" t="str">
-        <x:v/>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="J34" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K34" s="102" t="str">
-        <x:v/>
+        <x:v>按计划提交可验收证据</x:v>
       </x:c>
       <x:c r="L34" s="10"/>
       <x:c r="M34" s="102"/>
@@ -12484,9 +12500,8 @@
       <x:c r="J1" s="18"/>
     </x:row>
     <x:row r="2" spans="1:10" ht="20" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="6">
         <x:f>"数据截止"&amp;_数据接口!B5&amp;"。面向项目领导，重点呈现状态、风险、决策和未来两周行动。"</x:f>
-        <x:v>数据截止2026-09-24。面向项目领导，重点呈现状态、风险、决策和未来两周行动。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -12502,7 +12517,7 @@
       <x:c r="A3" s="7"/>
       <x:c r="B3" s="7" t="str">
         <x:f>'_数据接口'!B5</x:f>
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
       <x:c r="C3" s="7"/>
       <x:c r="D3" s="19"/>
@@ -12857,7 +12872,7 @@
       </x:c>
       <x:c r="B29" s="46">
         <x:f>IF('_数据接口'!B11=0,0,'_数据接口'!B22/'_数据接口'!B11)</x:f>
-        <x:v>0.06666666666666667</x:v>
+        <x:v>0.08888888888888889</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
         <x:v>294</x:v>
@@ -12876,7 +12891,7 @@
       </x:c>
       <x:c r="B30" s="48">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C30" s="33" t="s">
         <x:v>296</x:v>
@@ -12952,7 +12967,7 @@
       </x:c>
       <x:c r="B34" s="51">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C34" s="7" t="s">
         <x:v>301</x:v>
@@ -12966,9 +12981,16 @@
       <x:c r="J34" s="24"/>
     </x:row>
     <x:row r="35" spans="1:10" ht="20" customHeight="1">
-      <x:c r="A35" s="7"/>
-      <x:c r="B35" s="7"/>
-      <x:c r="C35" s="7"/>
+      <x:c r="A35" s="7" t="str">
+        <x:v>迭代承诺完成率</x:v>
+      </x:c>
+      <x:c r="B35" s="67">
+        <x:f>'_数据接口'!B44</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="str">
+        <x:v>周承诺兑现情况</x:v>
+      </x:c>
       <x:c r="D35" s="24"/>
       <x:c r="E35" s="24"/>
       <x:c r="F35" s="24"/>
@@ -12978,9 +13000,16 @@
       <x:c r="J35" s="24"/>
     </x:row>
     <x:row r="36" spans="1:10" ht="20" customHeight="1">
-      <x:c r="A36" s="7"/>
-      <x:c r="B36" s="7"/>
-      <x:c r="C36" s="7"/>
+      <x:c r="A36" s="7" t="str">
+        <x:v>迭代负载率</x:v>
+      </x:c>
+      <x:c r="B36" s="67">
+        <x:f>'_数据接口'!B45</x:f>
+        <x:v>1.3333</x:v>
+      </x:c>
+      <x:c r="C36" s="7" t="str">
+        <x:v>超100%为排产超负荷</x:v>
+      </x:c>
       <x:c r="D36" s="24"/>
       <x:c r="E36" s="24"/>
       <x:c r="F36" s="24"/>
@@ -12990,9 +13019,16 @@
       <x:c r="J36" s="24"/>
     </x:row>
     <x:row r="37" spans="1:10" ht="20" customHeight="1">
-      <x:c r="A37" s="7"/>
-      <x:c r="B37" s="7"/>
-      <x:c r="C37" s="7"/>
+      <x:c r="A37" s="7" t="str">
+        <x:v>预测超基线任务</x:v>
+      </x:c>
+      <x:c r="B37" s="7">
+        <x:f>'_数据接口'!B46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="7" t="str">
+        <x:v>预测完成晚于基线的任务数</x:v>
+      </x:c>
       <x:c r="D37" s="24"/>
       <x:c r="E37" s="24"/>
       <x:c r="F37" s="24"/>
@@ -13552,16 +13588,36 @@
       <x:c r="L14" s="12"/>
     </x:row>
     <x:row r="15" spans="1:12" ht="20" customHeight="1">
-      <x:c r="A15" s="7"/>
-      <x:c r="B15" s="11"/>
-      <x:c r="C15" s="7"/>
-      <x:c r="D15" s="12"/>
-      <x:c r="E15" s="7"/>
-      <x:c r="F15" s="7"/>
-      <x:c r="G15" s="7"/>
-      <x:c r="H15" s="7"/>
-      <x:c r="I15" s="7"/>
-      <x:c r="J15" s="7"/>
+      <x:c r="A15" s="7" t="str">
+        <x:v>RUN-20261016-001</x:v>
+      </x:c>
+      <x:c r="B15" s="97">
+        <x:v>46311.63607638889</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="str">
+        <x:v>全量刷新与质检</x:v>
+      </x:c>
+      <x:c r="D15" s="96">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>里程碑、总控、门禁、风险、决策、相关方及模块完整性</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="str">
+        <x:v>发现30项数据质量问题，其中5项阻断、25项需整改；17项任务已延期</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="str">
+        <x:v>优先处理阻断项，并由任务负责人补齐逾期任务的实际状态、日期和完成证据</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="str">
+        <x:v>待项目经理确认</x:v>
+      </x:c>
+      <x:c r="J15" s="7" t="str">
+        <x:v>项目经理</x:v>
+      </x:c>
       <x:c r="K15" s="7"/>
       <x:c r="L15" s="12"/>
     </x:row>
@@ -14843,7 +14899,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr/>
-  <x:dimension ref="A1:B43"/>
+  <x:dimension ref="A1:B48"/>
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <x:cols>
     <x:col min="1" max="1" width="20" customWidth="1"/>
@@ -14887,7 +14943,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2" ht="22" customHeight="1">
@@ -14967,7 +15023,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-10-16</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -15023,7 +15079,7 @@
         <x:v>已完成任务</x:v>
       </x:c>
       <x:c r="B22">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -15031,7 +15087,7 @@
         <x:v>进行中任务</x:v>
       </x:c>
       <x:c r="B23">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -15039,7 +15095,7 @@
         <x:v>未开始/待确认任务</x:v>
       </x:c>
       <x:c r="B24">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -15055,7 +15111,7 @@
         <x:v>平均进度</x:v>
       </x:c>
       <x:c r="B26">
-        <x:v>0.025925925925925925</x:v>
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -15063,7 +15119,7 @@
         <x:v>已延期任务</x:v>
       </x:c>
       <x:c r="B27">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -15183,6 +15239,43 @@
       </x:c>
       <x:c r="B43">
         <x:v>15252170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>迭代承诺完成率</x:v>
+      </x:c>
+      <x:c r="B44">
+        <x:v>0.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>迭代负载率</x:v>
+      </x:c>
+      <x:c r="B45">
+        <x:v>1.3333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>预测超基线任务数</x:v>
+      </x:c>
+      <x:c r="B46">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>平均偏差天数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>当前迭代周</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>2026-W40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO中心-20260920-V1.xlsx
@@ -2642,7 +2642,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4000,7 +4000,7 @@
         <x:v>统计日期</x:v>
       </x:c>
       <x:c r="B3" s="91">
-        <x:v>46311</x:v>
+        <x:v>46314</x:v>
       </x:c>
       <x:c r="C3" s="2"/>
       <x:c r="D3" s="2"/>
@@ -4082,12 +4082,15 @@
       </x:c>
       <x:c r="B6" s="57">
         <x:f>'_数据接口'!B22</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="57">
         <x:f>'_数据接口'!B23</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="57">
         <x:f>'_数据接口'!B24</x:f>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E6" s="57">
         <x:f>'_数据接口'!B25</x:f>
@@ -4095,6 +4098,7 @@
       </x:c>
       <x:c r="F6" s="58">
         <x:f>'_数据接口'!B26</x:f>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="G6" s="57">
         <x:f>'_数据接口'!B27</x:f>
@@ -4191,6 +4195,7 @@
     <x:row r="9" spans="1:14" ht="26" customHeight="1">
       <x:c r="A9" s="64">
         <x:f>'_数据接口'!B26</x:f>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="B9" s="65">
         <x:f>'_数据接口'!B17</x:f>
@@ -4304,6 +4309,7 @@
       </x:c>
       <x:c r="B12" s="7">
         <x:f>'_数据接口'!B22</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
         <x:v>83</x:v>
@@ -4343,6 +4349,7 @@
       </x:c>
       <x:c r="B13" s="7">
         <x:f>'_数据接口'!B23</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
         <x:v>90</x:v>
@@ -4382,6 +4389,7 @@
       </x:c>
       <x:c r="B14" s="2">
         <x:f>'_数据接口'!B24</x:f>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
         <x:v>98</x:v>
@@ -5016,7 +5024,7 @@
     <x:row r="2" spans="1:12" ht="20" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:f>"数据截止"&amp;'_数据接口'!B5&amp;"。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。"</x:f>
-        <x:v>数据截止2026-10-16。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。</x:v>
+        <x:v>数据截止2026-10-19。客观状态根据总控、风险和启动门禁快照形成，管理结论须由项目经理确认。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -5050,7 +5058,7 @@
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:f>'_数据接口'!B5</x:f>
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="7" t="s">
@@ -5126,7 +5134,7 @@
       </x:c>
       <x:c r="C7" s="2">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="20">
         <x:f>'_数据接口'!B28</x:f>
@@ -5220,7 +5228,7 @@
       </x:c>
       <x:c r="C11" s="2" t="str">
         <x:f>'_数据接口'!B27&amp;"项任务已延期或计划完成日已过"</x:f>
-        <x:v>17项任务已延期或计划完成日已过</x:v>
+        <x:v>26项任务已延期或计划完成日已过</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
         <x:v>153</x:v>
@@ -6644,34 +6652,34 @@
     </x:row>
     <x:row r="35" spans="1:10" ht="20" customHeight="1">
       <x:c r="A35" s="7" t="str">
-        <x:v/>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="B35" s="7" t="str">
-        <x:v/>
+        <x:v>T038</x:v>
       </x:c>
       <x:c r="C35" s="7" t="str">
-        <x:v/>
+        <x:v>完成启动条件检查与评审</x:v>
       </x:c>
       <x:c r="D35" s="7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="E35" s="96" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="F35" s="96" t="str">
-        <x:v/>
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="E35" s="96">
+        <x:v>46309</x:v>
+      </x:c>
+      <x:c r="F35" s="96">
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="G35" s="7" t="str">
-        <x:v/>
+        <x:v>计划完成日已过，执行状态和实际证据未确认</x:v>
       </x:c>
       <x:c r="H35" s="7" t="str">
-        <x:v/>
+        <x:v>需整改</x:v>
       </x:c>
       <x:c r="I35" s="7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="J35" s="7" t="str">
-        <x:v/>
+        <x:v>补充实际状态、实际日期、问题/阻塞及完成证据</x:v>
+      </x:c>
+      <x:c r="J35" s="7">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10" ht="20" customHeight="1">
@@ -9564,7 +9572,7 @@
         <x:v>46147</x:v>
       </x:c>
       <x:c r="H5" s="9">
-        <x:v>-164</x:v>
+        <x:v>-167</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9601,7 +9609,7 @@
         <x:v>46215</x:v>
       </x:c>
       <x:c r="H6" s="9">
-        <x:v>-96</x:v>
+        <x:v>-99</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9638,7 +9646,7 @@
         <x:v>46218</x:v>
       </x:c>
       <x:c r="H7" s="9">
-        <x:v>-93</x:v>
+        <x:v>-96</x:v>
       </x:c>
       <x:c r="I7" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9675,7 +9683,7 @@
         <x:v>46227</x:v>
       </x:c>
       <x:c r="H8" s="9">
-        <x:v>-84</x:v>
+        <x:v>-87</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9712,7 +9720,7 @@
         <x:v>46233</x:v>
       </x:c>
       <x:c r="H9" s="9">
-        <x:v>-78</x:v>
+        <x:v>-81</x:v>
       </x:c>
       <x:c r="I9" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9749,7 +9757,7 @@
         <x:v>46240</x:v>
       </x:c>
       <x:c r="H10" s="9">
-        <x:v>-71</x:v>
+        <x:v>-74</x:v>
       </x:c>
       <x:c r="I10" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9786,7 +9794,7 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="H11" s="9">
-        <x:v>-62</x:v>
+        <x:v>-65</x:v>
       </x:c>
       <x:c r="I11" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9823,7 +9831,7 @@
         <x:v>46252</x:v>
       </x:c>
       <x:c r="H12" s="9">
-        <x:v>-59</x:v>
+        <x:v>-62</x:v>
       </x:c>
       <x:c r="I12" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9860,7 +9868,7 @@
         <x:v>46253</x:v>
       </x:c>
       <x:c r="H13" s="9">
-        <x:v>-58</x:v>
+        <x:v>-61</x:v>
       </x:c>
       <x:c r="I13" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9897,7 +9905,7 @@
         <x:v>46258</x:v>
       </x:c>
       <x:c r="H14" s="9">
-        <x:v>-53</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="I14" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9934,7 +9942,7 @@
         <x:v>46263</x:v>
       </x:c>
       <x:c r="H15" s="9">
-        <x:v>-48</x:v>
+        <x:v>-51</x:v>
       </x:c>
       <x:c r="I15" s="9" t="str">
         <x:v>已延期</x:v>
@@ -9971,7 +9979,7 @@
         <x:v>46264</x:v>
       </x:c>
       <x:c r="H16" s="9">
-        <x:v>-47</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="I16" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10008,7 +10016,7 @@
         <x:v>46265</x:v>
       </x:c>
       <x:c r="H17" s="9">
-        <x:v>-46</x:v>
+        <x:v>-49</x:v>
       </x:c>
       <x:c r="I17" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10045,7 +10053,7 @@
         <x:v>46269</x:v>
       </x:c>
       <x:c r="H18" s="9">
-        <x:v>-42</x:v>
+        <x:v>-45</x:v>
       </x:c>
       <x:c r="I18" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10082,7 +10090,7 @@
         <x:v>46274</x:v>
       </x:c>
       <x:c r="H19" s="9">
-        <x:v>-37</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10119,7 +10127,7 @@
         <x:v>46279</x:v>
       </x:c>
       <x:c r="H20" s="9">
-        <x:v>-32</x:v>
+        <x:v>-35</x:v>
       </x:c>
       <x:c r="I20" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10156,7 +10164,7 @@
         <x:v>46279</x:v>
       </x:c>
       <x:c r="H21" s="9">
-        <x:v>-32</x:v>
+        <x:v>-35</x:v>
       </x:c>
       <x:c r="I21" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10193,7 +10201,7 @@
         <x:v>46284</x:v>
       </x:c>
       <x:c r="H22" s="9">
-        <x:v>-27</x:v>
+        <x:v>-30</x:v>
       </x:c>
       <x:c r="I22" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10230,7 +10238,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="H23" s="9">
-        <x:v>-21</x:v>
+        <x:v>-24</x:v>
       </x:c>
       <x:c r="I23" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10267,7 +10275,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="H24" s="9">
-        <x:v>-16</x:v>
+        <x:v>-19</x:v>
       </x:c>
       <x:c r="I24" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10304,7 +10312,7 @@
         <x:v>46297</x:v>
       </x:c>
       <x:c r="H25" s="9">
-        <x:v>-14</x:v>
+        <x:v>-17</x:v>
       </x:c>
       <x:c r="I25" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10341,7 +10349,7 @@
         <x:v>46300</x:v>
       </x:c>
       <x:c r="H26" s="9">
-        <x:v>-11</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="I26" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10378,7 +10386,7 @@
         <x:v>46303</x:v>
       </x:c>
       <x:c r="H27" s="9">
-        <x:v>-8</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10415,7 +10423,7 @@
         <x:v>46305</x:v>
       </x:c>
       <x:c r="H28" s="9">
-        <x:v>-6</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="I28" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10452,7 +10460,7 @@
         <x:v>46308</x:v>
       </x:c>
       <x:c r="H29" s="9">
-        <x:v>-3</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="I29" s="9" t="str">
         <x:v>已延期</x:v>
@@ -10489,16 +10497,16 @@
         <x:v>46311</x:v>
       </x:c>
       <x:c r="H30" s="9">
-        <x:v>0</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="I30" s="9" t="str">
-        <x:v>临近到期</x:v>
+        <x:v>已延期</x:v>
       </x:c>
       <x:c r="J30" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K30" s="102" t="str">
-        <x:v>按计划提交可验收证据</x:v>
+        <x:v>确认实际状态；完成、纠偏或提交基线变更</x:v>
       </x:c>
       <x:c r="L30" s="10"/>
       <x:c r="M30" s="102"/>
@@ -10526,10 +10534,10 @@
         <x:v>46315</x:v>
       </x:c>
       <x:c r="H31" s="9">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>临近到期</x:v>
       </x:c>
       <x:c r="J31" s="102" t="str">
         <x:v/>
@@ -10563,10 +10571,10 @@
         <x:v>46315</x:v>
       </x:c>
       <x:c r="H32" s="9">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I32" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>临近到期</x:v>
       </x:c>
       <x:c r="J32" s="102" t="str">
         <x:v/>
@@ -10600,10 +10608,10 @@
         <x:v>46315</x:v>
       </x:c>
       <x:c r="H33" s="9">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I33" s="9" t="str">
-        <x:v>正常</x:v>
+        <x:v>临近到期</x:v>
       </x:c>
       <x:c r="J33" s="102" t="str">
         <x:v/>
@@ -10637,7 +10645,7 @@
         <x:v>46321</x:v>
       </x:c>
       <x:c r="H34" s="9">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I34" s="9" t="str">
         <x:v>正常</x:v>
@@ -10653,37 +10661,37 @@
     </x:row>
     <x:row r="35" spans="1:13" ht="34" customHeight="1">
       <x:c r="A35" s="9" t="str">
-        <x:v/>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v/>
+        <x:v>T043</x:v>
       </x:c>
       <x:c r="C35" s="102" t="str">
-        <x:v/>
+        <x:v>形成需求清单并完成P0/P1/P2分级</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v/>
+        <x:v>MS008</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v/>
+        <x:v>未开始</x:v>
       </x:c>
       <x:c r="F35" s="9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="G35" s="95" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="H35" s="9" t="str">
-        <x:v/>
+        <x:v>产品经理</x:v>
+      </x:c>
+      <x:c r="G35" s="95">
+        <x:v>46328</x:v>
+      </x:c>
+      <x:c r="H35" s="9">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="9" t="str">
-        <x:v/>
+        <x:v>正常</x:v>
       </x:c>
       <x:c r="J35" s="102" t="str">
         <x:v/>
       </x:c>
       <x:c r="K35" s="102" t="str">
-        <x:v/>
+        <x:v>按计划提交可验收证据</x:v>
       </x:c>
       <x:c r="L35" s="10"/>
       <x:c r="M35" s="102"/>
@@ -12500,8 +12508,9 @@
       <x:c r="J1" s="18"/>
     </x:row>
     <x:row r="2" spans="1:10" ht="20" customHeight="1">
-      <x:c r="A2" s="6">
+      <x:c r="A2" s="6" t="str">
         <x:f>"数据截止"&amp;_数据接口!B5&amp;"。面向项目领导，重点呈现状态、风险、决策和未来两周行动。"</x:f>
+        <x:v>数据截止2026-10-19。面向项目领导，重点呈现状态、风险、决策和未来两周行动。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -12517,7 +12526,7 @@
       <x:c r="A3" s="7"/>
       <x:c r="B3" s="7" t="str">
         <x:f>'_数据接口'!B5</x:f>
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
       <x:c r="C3" s="7"/>
       <x:c r="D3" s="19"/>
@@ -12891,7 +12900,7 @@
       </x:c>
       <x:c r="B30" s="48">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C30" s="33" t="s">
         <x:v>296</x:v>
@@ -12967,7 +12976,7 @@
       </x:c>
       <x:c r="B34" s="51">
         <x:f>'_数据接口'!B27</x:f>
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C34" s="7" t="s">
         <x:v>301</x:v>
@@ -13622,16 +13631,36 @@
       <x:c r="L15" s="12"/>
     </x:row>
     <x:row r="16" spans="1:12" ht="20" customHeight="1">
-      <x:c r="A16" s="7"/>
-      <x:c r="B16" s="11"/>
-      <x:c r="C16" s="7"/>
-      <x:c r="D16" s="12"/>
-      <x:c r="E16" s="7"/>
-      <x:c r="F16" s="7"/>
-      <x:c r="G16" s="7"/>
-      <x:c r="H16" s="7"/>
-      <x:c r="I16" s="7"/>
-      <x:c r="J16" s="7"/>
+      <x:c r="A16" s="7" t="str">
+        <x:v>RUN-20261019-001</x:v>
+      </x:c>
+      <x:c r="B16" s="97">
+        <x:v>46314.594363425924</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="str">
+        <x:v>全量刷新与质检</x:v>
+      </x:c>
+      <x:c r="D16" s="96">
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>里程碑、总控、门禁、风险、决策、相关方及模块完整性</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="str">
+        <x:v>发现31项数据质量问题，其中5项阻断、26项需整改；26项任务已延期</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="str">
+        <x:v>优先处理阻断项，并由任务负责人补齐逾期任务的实际状态、日期和完成证据</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="str">
+        <x:v>待项目经理确认</x:v>
+      </x:c>
+      <x:c r="J16" s="7" t="str">
+        <x:v>项目经理</x:v>
+      </x:c>
       <x:c r="K16" s="7"/>
       <x:c r="L16" s="12"/>
     </x:row>
@@ -14943,7 +14972,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2" ht="22" customHeight="1">
@@ -15023,7 +15052,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
-        <x:v>2026-10-16</x:v>
+        <x:v>2026-10-19</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -15119,7 +15148,7 @@
         <x:v>已延期任务</x:v>
       </x:c>
       <x:c r="B27">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
